--- a/Data/TestingFile/匯入格式_客戶訂單_20260728001.xlsx
+++ b/Data/TestingFile/匯入格式_客戶訂單_20260728001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ImportDataToERP\Data\TestingFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ImportDataToERP\Data\TestingFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F386582-7868-4599-A22C-E3C3AD565740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998E2414-DEE7-4B59-953D-17947774B767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="574" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="574" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="批次匯入表" sheetId="1" r:id="rId1"/>
@@ -342,10 +342,6 @@
     <t>022</t>
   </si>
   <si>
-    <t>EC_KS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>備註(需要依照單身品項去對應到平台ORDER單號)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -413,6 +409,10 @@
   </si>
   <si>
     <t xml:space="preserve">DGB       </t>
+  </si>
+  <si>
+    <t>A01005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -628,10 +628,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="一般 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="一般 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="千分位" xfId="1" builtinId="3"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -647,7 +647,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -945,31 +945,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="工作表1"/>
   <dimension ref="A1:BM24"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="6"/>
-    <col min="2" max="2" width="18.5546875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="47.5546875" style="17" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="6"/>
+    <col min="2" max="2" width="18.54296875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="47.54296875" style="17" customWidth="1"/>
     <col min="7" max="7" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="7"/>
-    <col min="9" max="9" width="5.21875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" style="7"/>
+    <col min="9" max="9" width="5.1796875" style="7" customWidth="1"/>
     <col min="10" max="10" width="11" style="17" customWidth="1"/>
-    <col min="11" max="11" width="9.21875" style="7"/>
+    <col min="11" max="11" width="9.1796875" style="7"/>
     <col min="12" max="54" width="0" style="7" hidden="1" customWidth="1"/>
-    <col min="55" max="56" width="8.77734375" style="7" customWidth="1"/>
-    <col min="57" max="57" width="36.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.109375" style="7" customWidth="1"/>
-    <col min="59" max="59" width="10.77734375" style="7" customWidth="1"/>
-    <col min="60" max="61" width="9.21875" style="7"/>
-    <col min="62" max="62" width="10.77734375" style="7" customWidth="1"/>
+    <col min="55" max="56" width="8.81640625" style="7" customWidth="1"/>
+    <col min="57" max="57" width="36.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.08984375" style="7" customWidth="1"/>
+    <col min="59" max="59" width="10.81640625" style="7" customWidth="1"/>
+    <col min="60" max="61" width="9.1796875" style="7"/>
+    <col min="62" max="62" width="10.81640625" style="7" customWidth="1"/>
     <col min="63" max="63" width="12" style="22" customWidth="1"/>
-    <col min="64" max="16384" width="9.21875" style="7"/>
+    <col min="64" max="16384" width="9.1796875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" s="5" customFormat="1" ht="69" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" s="5" customFormat="1" ht="65" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>8</v>
@@ -1103,18 +1103,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B3" s="8">
         <v>220</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" s="16">
         <v>46022</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K3" s="7">
         <v>9</v>
@@ -1133,13 +1133,13 @@
         <v>220</v>
       </c>
       <c r="BD3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE3" t="s">
         <v>49</v>
       </c>
-      <c r="BE3" t="s">
-        <v>50</v>
-      </c>
       <c r="BG3" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH3">
         <v>1</v>
@@ -1157,12 +1157,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B4" s="8">
         <v>220</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>27</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K4" s="7">
         <v>9</v>
@@ -1188,10 +1188,10 @@
         <v>22</v>
       </c>
       <c r="BE4" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="BG4" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH4">
         <v>0</v>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="BM4" s="23"/>
     </row>
-    <row r="5" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B5" s="8">
         <v>220</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>27</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K5" s="7">
         <v>9</v>
@@ -1241,10 +1241,10 @@
         <v>23</v>
       </c>
       <c r="BE5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="BG5" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH5">
         <v>1</v>
@@ -1262,12 +1262,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B6" s="8">
         <v>220</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>27</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K6" s="7">
         <v>9</v>
@@ -1293,10 +1293,10 @@
         <v>24</v>
       </c>
       <c r="BE6" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="BG6" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH6">
         <v>1</v>
@@ -1314,12 +1314,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B7" s="8">
         <v>220</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>27</v>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K7" s="7">
         <v>9</v>
@@ -1345,10 +1345,10 @@
         <v>25</v>
       </c>
       <c r="BE7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG7" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH7">
         <v>0</v>
@@ -1366,12 +1366,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B8" s="8">
         <v>220</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>27</v>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K8" s="7">
         <v>9</v>
@@ -1397,10 +1397,10 @@
         <v>26</v>
       </c>
       <c r="BE8" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BG8" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH8">
         <v>1</v>
@@ -1418,12 +1418,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B9" s="8">
         <v>220</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>27</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K9" s="7">
         <v>9</v>
@@ -1449,10 +1449,10 @@
         <v>30</v>
       </c>
       <c r="BE9" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="BG9" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH9">
         <v>1</v>
@@ -1470,12 +1470,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B10" s="8">
         <v>220</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>27</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K10" s="7">
         <v>9</v>
@@ -1501,10 +1501,10 @@
         <v>31</v>
       </c>
       <c r="BE10" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="BG10" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH10">
         <v>0</v>
@@ -1522,12 +1522,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B11" s="8">
         <v>220</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>27</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K11" s="7">
         <v>9</v>
@@ -1553,10 +1553,10 @@
         <v>32</v>
       </c>
       <c r="BE11" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="BG11" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH11">
         <v>1</v>
@@ -1574,12 +1574,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B12" s="8">
         <v>220</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>27</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K12" s="7">
         <v>9</v>
@@ -1605,10 +1605,10 @@
         <v>33</v>
       </c>
       <c r="BE12" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="BG12" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH12" s="7">
         <v>1</v>
@@ -1626,12 +1626,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B13" s="8">
         <v>220</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>27</v>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K13" s="7">
         <v>9</v>
@@ -1657,10 +1657,10 @@
         <v>34</v>
       </c>
       <c r="BE13" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BG13" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH13" s="7">
         <v>1</v>
@@ -1678,12 +1678,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B14" s="8">
         <v>220</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>27</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K14" s="7">
         <v>9</v>
@@ -1709,10 +1709,10 @@
         <v>35</v>
       </c>
       <c r="BE14" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BG14" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH14" s="7">
         <v>1</v>
@@ -1730,12 +1730,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B15" s="8">
         <v>220</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>27</v>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K15" s="7">
         <v>9</v>
@@ -1761,10 +1761,10 @@
         <v>36</v>
       </c>
       <c r="BE15" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="BG15" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH15" s="7">
         <v>0</v>
@@ -1782,12 +1782,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:65" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="14" x14ac:dyDescent="0.25">
       <c r="B16" s="8">
         <v>220</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>27</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K16" s="7">
         <v>9</v>
@@ -1816,7 +1816,7 @@
         <v>3333</v>
       </c>
       <c r="BG16" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH16" s="7">
         <v>1</v>
@@ -1834,12 +1834,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:64" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:64" ht="14" x14ac:dyDescent="0.25">
       <c r="B17" s="8">
         <v>220</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>27</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K17" s="7">
         <v>9</v>
@@ -1868,7 +1868,7 @@
         <v>4444</v>
       </c>
       <c r="BG17" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH17" s="7">
         <v>1</v>
@@ -1886,12 +1886,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:64" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:64" ht="14" x14ac:dyDescent="0.25">
       <c r="B18" s="8">
         <v>220</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>27</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K18" s="7">
         <v>9</v>
@@ -1917,10 +1917,10 @@
         <v>39</v>
       </c>
       <c r="BE18" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BG18" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH18" s="7">
         <v>0</v>
@@ -1938,12 +1938,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="2:64" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:64" ht="14" x14ac:dyDescent="0.25">
       <c r="B19" s="8">
         <v>220</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>27</v>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K19" s="7">
         <v>9</v>
@@ -1969,10 +1969,10 @@
         <v>40</v>
       </c>
       <c r="BE19" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BG19" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH19" s="7">
         <v>1</v>
@@ -1990,12 +1990,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="2:64" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:64" ht="14" x14ac:dyDescent="0.25">
       <c r="B20" s="8">
         <v>220</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>27</v>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K20" s="7">
         <v>9</v>
@@ -2021,10 +2021,10 @@
         <v>41</v>
       </c>
       <c r="BE20" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BG20" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH20" s="7">
         <v>1</v>
@@ -2042,12 +2042,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:64" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:64" ht="14" x14ac:dyDescent="0.25">
       <c r="B21" s="8">
         <v>220</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>27</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K21" s="7">
         <v>9</v>
@@ -2076,7 +2076,7 @@
         <v>5555</v>
       </c>
       <c r="BG21" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH21" s="7">
         <v>0</v>
@@ -2094,12 +2094,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="2:64" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:64" ht="14" x14ac:dyDescent="0.25">
       <c r="B22" s="8">
         <v>220</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>27</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K22" s="7">
         <v>9</v>
@@ -2125,10 +2125,10 @@
         <v>43</v>
       </c>
       <c r="BE22" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="BG22" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH22" s="7">
         <v>1</v>
@@ -2146,12 +2146,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="2:64" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:64" ht="14" x14ac:dyDescent="0.25">
       <c r="B23" s="8">
         <v>220</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>27</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K23" s="7">
         <v>9</v>
@@ -2180,7 +2180,7 @@
         <v>6666</v>
       </c>
       <c r="BG23" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BH23" s="7">
         <v>1</v>
@@ -2198,12 +2198,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="2:64" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:64" ht="14" x14ac:dyDescent="0.25">
       <c r="B24" s="8">
         <v>220</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>27</v>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="16">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="K24" s="7">
         <v>9</v>
@@ -2229,10 +2229,10 @@
         <v>45</v>
       </c>
       <c r="BE24" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="BG24" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="BG24" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="BH24" s="7">
         <v>1</v>
